--- a/Data Files/OTM Test Data/Driver IDs data.xlsx
+++ b/Data Files/OTM Test Data/Driver IDs data.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GauravPrasad\Desktop\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{FC903A31-2400-48EB-A6AF-EC0ECC039D07}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2850C0-801A-425F-9AA4-BDCFDD2984BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{19177B12-2342-4277-B5D8-90C83045BD68}" yWindow="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{19177B12-2342-4277-B5D8-90C83045BD68}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Reference No.</t>
   </si>
@@ -41,24 +41,11 @@
   <si>
     <t>LEO_GUISE_20059805</t>
   </si>
-  <si>
-    <t>Ref No. is already present</t>
-  </si>
-  <si>
-    <t>20061210</t>
-  </si>
-  <si>
-    <t>20059805</t>
-  </si>
-  <si>
-    <t>Success</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -115,24 +102,24 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -149,10 +136,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -187,7 +174,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -239,7 +226,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -350,21 +337,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -381,7 +368,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -433,20 +420,20 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D655408-AE02-469F-ACDF-59509441D3E8}">
-  <dimension ref="A1:D8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D655408-AE02-469F-ACDF-59509441D3E8}">
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="32.26953125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="17.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="46.26953125" collapsed="true"/>
+    <col min="1" max="1" width="32.26953125" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="17.453125" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="46.26953125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -464,23 +451,15 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
@@ -509,9 +488,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink display="javascript:void(0);" r:id="rId1" ref="A3" xr:uid="{E6001E7B-9A87-4A0C-B763-850052F5F25F}"/>
+    <hyperlink ref="A3" r:id="rId1" display="javascript:void(0);" xr:uid="{E6001E7B-9A87-4A0C-B763-850052F5F25F}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>